--- a/makeup_forms/047_makeup_appointment_form--makeup_forms.xlsx
+++ b/makeup_forms/047_makeup_appointment_form--makeup_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -681,7 +681,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>appointment_time</t>
+          <t>appointment_time_2</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -704,7 +704,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>appointment_date</t>
+          <t>appointment_date_2</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -778,7 +778,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Status</t>
+          <t>Make Up Status</t>
         </is>
       </c>
       <c r="D15" t="inlineStr"/>
@@ -865,12 +865,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>appointment_time_2</t>
+          <t>appointment_time_2_2</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Time</t>
+          <t>Appointment Time 2 2</t>
         </is>
       </c>
       <c r="D19" t="inlineStr"/>
@@ -888,7 +888,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>appointment_date_2</t>
+          <t>appointment_date_2_2</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -916,7 +916,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Status</t>
+          <t>Appointment Status 3</t>
         </is>
       </c>
       <c r="D21" t="inlineStr"/>
@@ -939,7 +939,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Make up Services</t>
+          <t>Make Up Services 4</t>
         </is>
       </c>
       <c r="D22" t="inlineStr"/>
@@ -962,7 +962,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Status</t>
+          <t>Make Up Status 2</t>
         </is>
       </c>
       <c r="D23" t="inlineStr"/>
@@ -985,7 +985,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Time</t>
+          <t>Make Up Time 2</t>
         </is>
       </c>
       <c r="D24" t="inlineStr"/>
@@ -1008,7 +1008,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Date</t>
+          <t>Appointment Date 3</t>
         </is>
       </c>
       <c r="D25" t="inlineStr"/>
@@ -1031,7 +1031,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Special Request</t>
+          <t>Make Up Request</t>
         </is>
       </c>
       <c r="D26" t="inlineStr"/>
@@ -1054,7 +1054,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Status</t>
+          <t>Appointment Status 4</t>
         </is>
       </c>
       <c r="D27" t="inlineStr"/>
@@ -1077,7 +1077,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Make up Services</t>
+          <t>Make Up Services 5</t>
         </is>
       </c>
       <c r="D28" t="inlineStr"/>
@@ -1262,7 +1262,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>appointment_time_choices</t>
+          <t>appointment_time_2_choices</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1279,7 +1279,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>appointment_time_choices</t>
+          <t>appointment_time_2_choices</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1296,7 +1296,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>appointment_date_choices</t>
+          <t>appointment_date_2_choices</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1313,7 +1313,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>appointment_date_choices</t>
+          <t>appointment_date_2_choices</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1500,7 +1500,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>appointment_time_2_choices</t>
+          <t>appointment_time_2_2_choices</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1517,7 +1517,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>appointment_time_2_choices</t>
+          <t>appointment_time_2_2_choices</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1534,7 +1534,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>appointment_date_2_choices</t>
+          <t>appointment_date_2_2_choices</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -1551,7 +1551,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>appointment_date_2_choices</t>
+          <t>appointment_date_2_2_choices</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
